--- a/data/trans_orig/Q02D_LAB-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,51</t>
+          <t>2,35; 3,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 5,21</t>
+          <t>4,15; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,87</t>
+          <t>5,27; 6,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,58</t>
+          <t>5,01; 8,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,47</t>
+          <t>4,06; 5,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,13</t>
+          <t>6,22; 7,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,77</t>
+          <t>7,11; 8,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,27</t>
+          <t>7,09; 10,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,51</t>
+          <t>3,58; 4,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 6,22</t>
+          <t>5,48; 6,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,68</t>
+          <t>6,42; 7,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,99</t>
+          <t>6,6; 8,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,69</t>
+          <t>3,28; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 5,41</t>
+          <t>4,57; 5,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,8</t>
+          <t>4,61; 5,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,78</t>
+          <t>4,28; 6,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,62</t>
+          <t>5,28; 6,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,06</t>
+          <t>6,16; 6,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,12</t>
+          <t>6,89; 8,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 7,93</t>
+          <t>6,35; 8,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,62</t>
+          <t>4,59; 5,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,23</t>
+          <t>5,66; 6,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,04</t>
+          <t>6,11; 7,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,27</t>
+          <t>5,85; 7,18</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,88</t>
+          <t>3,57; 4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,12</t>
+          <t>4,32; 5,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,68</t>
+          <t>6,86; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 12,24</t>
+          <t>4,2; 11,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,17</t>
+          <t>5,66; 7,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,24</t>
+          <t>6,4; 7,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,44</t>
+          <t>9,5; 11,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 10,63</t>
+          <t>7,31; 10,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,07</t>
+          <t>4,95; 6,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,36</t>
+          <t>5,69; 6,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,07</t>
+          <t>8,74; 10,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,84</t>
+          <t>6,73; 10,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,44</t>
+          <t>3,08; 4,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,0</t>
+          <t>4,1; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,71</t>
+          <t>6,01; 7,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,79</t>
+          <t>4,33; 7,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,06</t>
+          <t>5,67; 7,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 6,82</t>
+          <t>6,04; 6,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,31</t>
+          <t>7,86; 9,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,4</t>
+          <t>5,92; 8,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,86</t>
+          <t>4,82; 5,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 5,97</t>
+          <t>5,36; 5,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,47</t>
+          <t>7,31; 8,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,54</t>
+          <t>5,53; 7,49</t>
         </is>
       </c>
     </row>
@@ -1276,27 +1276,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,03</t>
+          <t>3,32; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 4,97</t>
+          <t>4,49; 4,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,67</t>
+          <t>5,9; 6,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,97</t>
+          <t>5,08; 6,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,22</t>
+          <t>5,43; 6,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 8,87</t>
+          <t>8,1; 8,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,2</t>
+          <t>7,02; 8,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,24</t>
+          <t>4,73; 5,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,02</t>
+          <t>5,7; 6,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,85</t>
+          <t>7,31; 7,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,52</t>
+          <t>6,45; 7,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_LAB-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,35</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,61</t>
+          <t>2,38; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,26</t>
+          <t>4,12; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,97</t>
+          <t>5,26; 6,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,41</t>
+          <t>4,82; 8,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,36</t>
+          <t>4,06; 5,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,13</t>
+          <t>6,2; 7,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,81</t>
+          <t>7,13; 8,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,39</t>
+          <t>7,0; 10,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,5</t>
+          <t>3,55; 4,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,21</t>
+          <t>5,46; 6,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,71</t>
+          <t>6,52; 7,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 8,86</t>
+          <t>6,32; 8,74</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,71</t>
+          <t>3,28; 4,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,4</t>
+          <t>4,56; 5,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,82</t>
+          <t>4,65; 5,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,81</t>
+          <t>4,46; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,67</t>
+          <t>5,34; 6,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 6,99</t>
+          <t>6,21; 7,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,1</t>
+          <t>6,87; 8,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,0</t>
+          <t>6,35; 7,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,61</t>
+          <t>4,64; 5,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 6,27</t>
+          <t>5,63; 6,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,02</t>
+          <t>6,1; 6,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,18</t>
+          <t>5,82; 7,2</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,65</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,09</t>
+          <t>7,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,96</t>
+          <t>3,53; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,17</t>
+          <t>4,26; 5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,71</t>
+          <t>6,83; 8,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,82</t>
+          <t>4,31; 11,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,15</t>
+          <t>5,62; 7,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 7,27</t>
+          <t>6,38; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 11,27</t>
+          <t>9,57; 11,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,58</t>
+          <t>7,39; 10,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,12</t>
+          <t>4,99; 6,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,36</t>
+          <t>5,71; 6,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 10,02</t>
+          <t>8,78; 10,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,02</t>
+          <t>6,79; 9,62</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,61</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,2</t>
+          <t>3,04; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,0</t>
+          <t>4,06; 4,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,6</t>
+          <t>5,96; 7,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,73</t>
+          <t>4,24; 6,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,0</t>
+          <t>5,61; 7,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 6,79</t>
+          <t>6,04; 6,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 9,29</t>
+          <t>7,78; 9,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,55</t>
+          <t>6,33; 8,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,75</t>
+          <t>4,82; 5,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,4</t>
+          <t>7,27; 8,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,49</t>
+          <t>5,78; 7,88</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1223,14 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,82</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,6</t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,67</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>6,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,0</t>
+          <t>3,35; 4,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 4,94</t>
+          <t>4,5; 4,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,7</t>
+          <t>5,89; 6,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,92</t>
+          <t>5,03; 6,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,19</t>
+          <t>5,51; 6,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,82</t>
+          <t>6,41; 6,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 8,86</t>
+          <t>8,14; 8,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,24</t>
+          <t>7,1; 8,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,25</t>
+          <t>4,72; 5,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,01</t>
+          <t>5,7; 6,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,89</t>
+          <t>7,29; 7,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,49</t>
+          <t>6,47; 7,45</t>
         </is>
       </c>
     </row>
